--- a/backend/data/excel/a23adaca0683_data.xlsx
+++ b/backend/data/excel/a23adaca0683_data.xlsx
@@ -472,7 +472,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>도시형생활주택 인허가 실적 - 도시형생활주택 인허가 실적 (201302 ~ 202508)</t>
+          <t>도시형생활주택 인허가 실적 - 도시형생활주택 인허가 실적 (201302 ~ 202509)</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>도시형생활주택 인허가 실적 (201302 ~ 202508)</t>
+          <t>도시형생활주택 인허가 실적 (201302 ~ 202509)</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2025-10-17 05:02:36</t>
+          <t>2025-10-31 13:45:44</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>도시형생활주택 인허가 실적 / 도시형생활주택 인허가 실적 (201302 ~ 202508)</t>
+          <t>도시형생활주택 인허가 실적 / 도시형생활주택 인허가 실적 (201302 ~ 202509)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>도시형생활주택 인허가 실적 (201302 ~ 202508)</t>
+          <t>도시형생활주택 인허가 실적 (201302 ~ 202509)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>다운로드 시간 : 2025-10-17   04:55</t>
+          <t>다운로드 시간 : 2025-10-31   13:41</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -919,13 +919,13 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>도시형생활주택 인허가 실적 (201302 ~ 202508)</t>
+          <t>도시형생활주택 인허가 실적 (201302 ~ 202509)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>검색기간  : 202508 ~ 202508</t>
+          <t>검색기간  : 202509 ~ 202509</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>도시형생활주택 인허가 실적 (201302 ~ 202508)</t>
+          <t>도시형생활주택 인허가 실적 (201302 ~ 202509)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>도시형생활주택 인허가 실적 (201302 ~ 202508)</t>
+          <t>도시형생활주택 인허가 실적 (201302 ~ 202509)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>도시형생활주택 인허가 실적 (201302 ~ 202508)</t>
+          <t>도시형생활주택 인허가 실적 (201302 ~ 202509)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>도시형생활주택 인허가 실적 (201302 ~ 202508)</t>
+          <t>도시형생활주택 인허가 실적 (201302 ~ 202509)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1114,42 +1114,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>1,117</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>335</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>377</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>405</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5,227</t>
+          <t>6,344</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1,205</t>
+          <t>1,540</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2,519</t>
+          <t>2,896</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1,503</t>
+          <t>1,908</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>도시형생활주택 인허가 실적 (201302 ~ 202508)</t>
+          <t>도시형생활주택 인허가 실적 (201302 ~ 202509)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1174,42 +1174,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>690</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>308</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>280</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>102</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2,739</t>
+          <t>3,429</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>924</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1,768</t>
+          <t>2,048</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>457</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>도시형생활주택 인허가 실적 (201302 ~ 202508)</t>
+          <t>도시형생활주택 인허가 실적 (201302 ~ 202509)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1244,12 +1244,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>도시형생활주택 인허가 실적 (201302 ~ 202508)</t>
+          <t>도시형생활주택 인허가 실적 (201302 ~ 202509)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>도시형생활주택 인허가 실적 (201302 ~ 202508)</t>
+          <t>도시형생활주택 인허가 실적 (201302 ~ 202509)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>80</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>64</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>324</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>264</t>
         </is>
       </c>
     </row>
@@ -1399,12 +1399,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>도시형생활주택 인허가 실적 (201302 ~ 202508)</t>
+          <t>도시형생활주택 인허가 실적 (201302 ~ 202509)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>111</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>111</t>
         </is>
       </c>
     </row>
@@ -1459,12 +1459,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>도시형생활주택 인허가 실적 (201302 ~ 202508)</t>
+          <t>도시형생활주택 인허가 실적 (201302 ~ 202509)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1519,12 +1519,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>도시형생활주택 인허가 실적 (201302 ~ 202508)</t>
+          <t>도시형생활주택 인허가 실적 (201302 ~ 202509)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>도시형생활주택 인허가 실적 (201302 ~ 202508)</t>
+          <t>도시형생활주택 인허가 실적 (201302 ~ 202509)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1639,12 +1639,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>도시형생활주택 인허가 실적 (201302 ~ 202508)</t>
+          <t>도시형생활주택 인허가 실적 (201302 ~ 202509)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1654,27 +1654,27 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>129</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>64</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>1,010</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1684,12 +1684,12 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>562</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>319</t>
         </is>
       </c>
     </row>
@@ -1699,12 +1699,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>도시형생활주택 인허가 실적 (201302 ~ 202508)</t>
+          <t>도시형생활주택 인허가 실적 (201302 ~ 202509)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1734,12 +1734,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>96</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>도시형생활주택 인허가 실적 (201302 ~ 202508)</t>
+          <t>도시형생활주택 인허가 실적 (201302 ~ 202509)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1819,12 +1819,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>도시형생활주택 인허가 실적 (201302 ~ 202508)</t>
+          <t>도시형생활주택 인허가 실적 (201302 ~ 202509)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>도시형생활주택 인허가 실적 (201302 ~ 202508)</t>
+          <t>도시형생활주택 인허가 실적 (201302 ~ 202509)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>도시형생활주택 인허가 실적 (201302 ~ 202508)</t>
+          <t>도시형생활주택 인허가 실적 (201302 ~ 202509)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>도시형생활주택 인허가 실적 (201302 ~ 202508)</t>
+          <t>도시형생활주택 인허가 실적 (201302 ~ 202509)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2059,12 +2059,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>도시형생활주택 인허가 실적 (201302 ~ 202508)</t>
+          <t>도시형생활주택 인허가 실적 (201302 ~ 202509)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>도시형생활주택 인허가 실적 (201302 ~ 202508)</t>
+          <t>도시형생활주택 인허가 실적 (201302 ~ 202509)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>116</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2144,17 +2144,17 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>99</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>382</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>109</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>273</t>
         </is>
       </c>
     </row>
